--- a/data/trans_camb/P2A_enfcro_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,17; 16,73</t>
+          <t>8,68; 16,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 11,16</t>
+          <t>2,33; 10,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,0; -3,67</t>
+          <t>-14,38; -4,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 12,83</t>
+          <t>6,71; 12,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 11,42</t>
+          <t>4,85; 11,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,56; -8,73</t>
+          <t>-15,35; -8,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,76; 13,78</t>
+          <t>8,81; 13,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 10,17</t>
+          <t>4,8; 10,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,26; -7,28</t>
+          <t>-13,27; -7,33</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,83; 27,69</t>
+          <t>13,34; 27,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 18,23</t>
+          <t>3,75; 18,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-21,83; -6,03</t>
+          <t>-22,13; -6,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,84; 17,37</t>
+          <t>8,67; 17,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,98; 15,51</t>
+          <t>6,27; 15,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-20,09; -11,5</t>
+          <t>-19,86; -11,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,2; 19,94</t>
+          <t>12,31; 20,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 14,83</t>
+          <t>6,77; 15,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,67; -10,49</t>
+          <t>-18,6; -10,59</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,95</t>
+          <t>6,83; 13,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 13,19</t>
+          <t>6,57; 13,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,06; -2,58</t>
+          <t>-15,02; -2,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,7; 10,66</t>
+          <t>3,66; 10,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 6,75</t>
+          <t>0,16; 6,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 5,31</t>
+          <t>-18,73; 4,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,37</t>
+          <t>6,2; 10,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,73; 9,39</t>
+          <t>4,53; 9,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 0,84</t>
+          <t>-14,6; 0,51</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17,89; 38,38</t>
+          <t>18,46; 39,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,55; 39,14</t>
+          <t>17,48; 39,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-44,56; -7,47</t>
+          <t>-42,23; -8,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 21,88</t>
+          <t>6,62; 21,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 13,77</t>
+          <t>0,31; 14,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,46; 10,44</t>
+          <t>-36,64; 9,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,5; 24,84</t>
+          <t>14,04; 26,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,72; 22,6</t>
+          <t>10,37; 23,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,66; 2,04</t>
+          <t>-33,85; 1,74</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 14,55</t>
+          <t>0,93; 14,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 8,27</t>
+          <t>-4,5; 8,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,8; -3,34</t>
+          <t>-15,2; -3,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 9,16</t>
+          <t>-4,67; 8,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 2,52</t>
+          <t>-9,54; 2,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,13; -14,46</t>
+          <t>-25,24; -13,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 9,98</t>
+          <t>0,52; 9,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 4,06</t>
+          <t>-4,95; 3,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,92; -9,76</t>
+          <t>-18,28; -10,42</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,98; 42,92</t>
+          <t>2,51; 44,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 24,17</t>
+          <t>-10,75; 23,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-36,89; -10,5</t>
+          <t>-37,1; -11,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 19,56</t>
+          <t>-8,62; 17,16</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 5,35</t>
+          <t>-17,98; 6,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,51; -30,65</t>
+          <t>-47,24; -29,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 24,32</t>
+          <t>1,15; 24,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 9,9</t>
+          <t>-10,97; 9,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-39,59; -24,14</t>
+          <t>-39,92; -25,11</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,94</t>
+          <t>7,23; 12,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,76</t>
+          <t>2,94; 8,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,62; -8,76</t>
+          <t>-19,85; -8,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 9,43</t>
+          <t>4,79; 9,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 3,42</t>
+          <t>-1,32; 3,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,13; -6,0</t>
+          <t>-22,26; -5,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,57; 10,16</t>
+          <t>6,66; 10,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,0</t>
+          <t>1,48; 4,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,85; -9,34</t>
+          <t>-18,93; -9,48</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,84; 27,43</t>
+          <t>15,95; 28,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,24; 18,16</t>
+          <t>6,4; 18,49</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-44,15; -20,16</t>
+          <t>-43,63; -20,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8,25; 16,03</t>
+          <t>7,8; 15,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 5,75</t>
+          <t>-2,16; 5,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,4; -10,09</t>
+          <t>-36,47; -9,74</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,31; 19,69</t>
+          <t>12,51; 19,57</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,63; 9,72</t>
+          <t>2,79; 9,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-35,86; -18,12</t>
+          <t>-35,73; -18,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-9,03</t>
+          <t>-12,46</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-12,07</t>
+          <t>-12,99</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-10,38</t>
+          <t>-12,42</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,68; 16,45</t>
+          <t>8,8; 16,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 10,87</t>
+          <t>1,99; 11,33</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,38; -4,0</t>
+          <t>-17,72; -7,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,71; 12,75</t>
+          <t>6,77; 12,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,43</t>
+          <t>5,02; 11,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,35; -8,42</t>
+          <t>-16,54; -9,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,81; 13,86</t>
+          <t>8,79; 13,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 10,4</t>
+          <t>4,72; 10,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,27; -7,33</t>
+          <t>-15,21; -9,22</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-14,37%</t>
+          <t>-19,83%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-15,89%</t>
+          <t>-17,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-14,8%</t>
+          <t>-17,7%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,34; 27,23</t>
+          <t>13,53; 28,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,75; 18,03</t>
+          <t>3,21; 18,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-22,13; -6,29</t>
+          <t>-27,36; -12,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,67; 17,09</t>
+          <t>8,75; 17,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,27; 15,38</t>
+          <t>6,49; 15,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,86; -11,45</t>
+          <t>-21,38; -12,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,31; 20,18</t>
+          <t>12,24; 20,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,77; 15,16</t>
+          <t>6,75; 15,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-18,6; -10,59</t>
+          <t>-21,45; -13,47</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-7,22</t>
+          <t>-5,11</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-11,24</t>
+          <t>-16,35</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-9,05</t>
+          <t>-10,51</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 13,18</t>
+          <t>6,51; 13,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 13,19</t>
+          <t>6,95; 13,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,02; -2,74</t>
+          <t>-8,04; -1,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 10,71</t>
+          <t>3,8; 10,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 6,89</t>
+          <t>0,17; 6,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 4,75</t>
+          <t>-19,84; -13,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,2; 10,92</t>
+          <t>5,95; 10,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,53; 9,52</t>
+          <t>4,61; 9,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 0,51</t>
+          <t>-12,85; -8,34</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-20,39%</t>
+          <t>-14,44%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-22,22%</t>
+          <t>-32,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-21,17%</t>
+          <t>-24,6%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,46; 39,11</t>
+          <t>17,57; 39,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,48; 39,67</t>
+          <t>19,06; 41,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-42,23; -8,01</t>
+          <t>-21,78; -5,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 21,91</t>
+          <t>7,23; 21,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,31; 14,06</t>
+          <t>0,33; 14,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,64; 9,89</t>
+          <t>-37,78; -27,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,04; 26,62</t>
+          <t>13,73; 26,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,37; 23,26</t>
+          <t>10,41; 22,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 1,74</t>
+          <t>-29,18; -20,0</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-9,33</t>
+          <t>-10,1</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-20,01</t>
+          <t>-20,23</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-14,2</t>
+          <t>-14,68</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 14,66</t>
+          <t>2,35; 14,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 8,18</t>
+          <t>-4,57; 7,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,2; -3,95</t>
+          <t>-15,17; -3,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 8,03</t>
+          <t>-4,95; 8,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 2,89</t>
+          <t>-10,09; 2,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,24; -13,64</t>
+          <t>-25,91; -15,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 9,85</t>
+          <t>0,71; 10,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 3,65</t>
+          <t>-4,91; 3,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-18,28; -10,42</t>
+          <t>-18,5; -10,69</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-24,9%</t>
+          <t>-26,97%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-39,89%</t>
+          <t>-40,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-32,75%</t>
+          <t>-33,86%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,51; 44,33</t>
+          <t>5,8; 43,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 23,72</t>
+          <t>-11,34; 21,88</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-37,1; -11,39</t>
+          <t>-38,04; -10,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 17,16</t>
+          <t>-9,19; 19,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-17,98; 6,03</t>
+          <t>-18,58; 5,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,24; -29,82</t>
+          <t>-48,42; -32,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 24,24</t>
+          <t>1,58; 24,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 9,22</t>
+          <t>-10,8; 9,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-39,92; -25,11</t>
+          <t>-40,56; -26,17</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-12,39</t>
+          <t>-11,38</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-17,64</t>
+          <t>-20,68</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-14,98</t>
+          <t>-16,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,25</t>
+          <t>6,95; 11,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,04</t>
+          <t>2,81; 7,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,85; -8,99</t>
+          <t>-14,04; -9,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,28</t>
+          <t>4,67; 9,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,31</t>
+          <t>-1,2; 3,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-22,26; -5,87</t>
+          <t>-22,88; -18,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,66; 10,06</t>
+          <t>6,63; 10,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,88</t>
+          <t>1,61; 4,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -9,48</t>
+          <t>-17,67; -14,45</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-27,91%</t>
+          <t>-25,66%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-29,21%</t>
+          <t>-34,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-28,54%</t>
+          <t>-30,58%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,95; 28,45</t>
+          <t>15,21; 27,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,4; 18,49</t>
+          <t>6,26; 17,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,63; -20,41</t>
+          <t>-30,87; -21,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7,8; 15,79</t>
+          <t>7,64; 16,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 5,59</t>
+          <t>-1,96; 5,83</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,47; -9,74</t>
+          <t>-37,24; -31,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,51; 19,57</t>
+          <t>12,44; 19,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,46</t>
+          <t>2,94; 9,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-35,73; -18,09</t>
+          <t>-33,26; -28,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_enfcro_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_enfcro_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Población que convive con personas con enfermedades crónicas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
